--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C23DE9-AD05-4869-A0B5-04BC72CD0E65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD1768D-6738-4696-9086-8A2D1E479D81}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ammoniaBAU" sheetId="1" r:id="rId1"/>
@@ -989,6 +989,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
@@ -2311,7 +2314,6 @@
         <v>0.22732990360056848</v>
       </c>
       <c r="F2" s="3">
-        <f>ammoniaBlue!D2-ammoniaBlue!E2-SUM(ammoniaBlue!G2:N2)</f>
         <v>0.32145189616086728</v>
       </c>
     </row>
@@ -2332,7 +2334,6 @@
         <v>0.22732990410790538</v>
       </c>
       <c r="F3" s="3">
-        <f>ammoniaBlue!D3-ammoniaBlue!E3-SUM(ammoniaBlue!G3:N3)</f>
         <v>0.3126381995602498</v>
       </c>
     </row>
@@ -2353,7 +2354,6 @@
         <v>0.22732990470400433</v>
       </c>
       <c r="F4" s="3">
-        <f>ammoniaBlue!D4-ammoniaBlue!E4-SUM(ammoniaBlue!G4:N4)</f>
         <v>0.30159400439014816</v>
       </c>
     </row>
@@ -2374,7 +2374,6 @@
         <v>0.22732990563664224</v>
       </c>
       <c r="F5" s="3">
-        <f>ammoniaBlue!D5-ammoniaBlue!E5-SUM(ammoniaBlue!G5:N5)</f>
         <v>0.28410944139127103</v>
       </c>
     </row>
@@ -2395,7 +2394,6 @@
         <v>0.22732991229465516</v>
       </c>
       <c r="F6" s="3">
-        <f>ammoniaBlue!D6-ammoniaBlue!E6-SUM(ammoniaBlue!G6:N6)</f>
         <v>0.16284495701298385</v>
       </c>
     </row>
@@ -2416,7 +2414,6 @@
         <v>0.22732991448354031</v>
       </c>
       <c r="F7" s="3">
-        <f>ammoniaBlue!D7-ammoniaBlue!E7-SUM(ammoniaBlue!G7:N7)</f>
         <v>0.12260248912663135</v>
       </c>
     </row>
@@ -2437,7 +2434,6 @@
         <v>0.22732991508593314</v>
       </c>
       <c r="F8" s="3">
-        <f>ammoniaBlue!D8-ammoniaBlue!E8-SUM(ammoniaBlue!G8:N8)</f>
         <v>0.11153771499438864</v>
       </c>
     </row>
@@ -2458,7 +2454,6 @@
         <v>0.22732990626591718</v>
       </c>
       <c r="F9" s="3">
-        <f>ammoniaBlue!D9-ammoniaBlue!E9-SUM(ammoniaBlue!G9:N9)</f>
         <v>0.27315404096324064</v>
       </c>
     </row>
@@ -2479,7 +2474,6 @@
         <v>0.22732991145288048</v>
       </c>
       <c r="F10" s="3">
-        <f>ammoniaBlue!D10-ammoniaBlue!E10-SUM(ammoniaBlue!G10:N10)</f>
         <v>0.17776204914569982</v>
       </c>
     </row>
@@ -2500,7 +2494,6 @@
         <v>0.22732991466453067</v>
       </c>
       <c r="F11" s="3">
-        <f>ammoniaBlue!D11-ammoniaBlue!E11-SUM(ammoniaBlue!G11:N11)</f>
         <v>0.11889851912889865</v>
       </c>
     </row>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4DF0F3-361C-46CD-A52A-CFB10A183183}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717BB783-A931-4BFB-AC06-DBEAC39D5932}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ammoniaBAU" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -206,10 +206,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1027,13 +1027,13 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0.92462100700611893</v>
+        <v>0.84544352929668787</v>
       </c>
       <c r="E2">
         <v>0.17700465064266549</v>
       </c>
       <c r="F2">
-        <v>0.28722738742945769</v>
+        <v>0.20804991150944696</v>
       </c>
       <c r="G2">
         <v>0.16072383870141799</v>
@@ -1057,7 +1057,7 @@
         <v>8.5862083956007706E-3</v>
       </c>
       <c r="N2">
-        <v>0.22688939700836835</v>
+        <v>0.22688939521894802</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1071,13 +1071,13 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>0.90566818660393866</v>
+        <v>0.82972722567453527</v>
       </c>
       <c r="E3">
         <v>0.17536524668211859</v>
       </c>
       <c r="F3">
-        <v>0.28084526839092816</v>
+        <v>0.20490430917779914</v>
       </c>
       <c r="G3">
         <v>0.15472803085744799</v>
@@ -1101,7 +1101,7 @@
         <v>8.2613248684330239E-3</v>
       </c>
       <c r="N3">
-        <v>0.22688939721581924</v>
+        <v>0.22688939549954487</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1115,13 +1115,13 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>0.88757066968595177</v>
+        <v>0.81619603201693336</v>
       </c>
       <c r="E4">
         <v>0.17422970254303261</v>
       </c>
       <c r="F4">
-        <v>0.2735714350148048</v>
+        <v>0.20219679895886142</v>
       </c>
       <c r="G4">
         <v>0.14673221540162251</v>
@@ -1145,7 +1145,7 @@
         <v>7.8256100419213537E-3</v>
       </c>
       <c r="N4">
-        <v>0.22688939741515596</v>
+        <v>0.22688939580208092</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1159,13 +1159,13 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>0.86271790818599037</v>
+        <v>0.79918499426740519</v>
       </c>
       <c r="E5">
         <v>0.17347749469097129</v>
       </c>
       <c r="F5">
-        <v>0.26314843079700617</v>
+        <v>0.19961551831427121</v>
       </c>
       <c r="G5">
         <v>0.13355943110288879</v>
@@ -1189,7 +1189,7 @@
         <v>7.124646457739239E-3</v>
       </c>
       <c r="N5">
-        <v>0.22688939769529071</v>
+        <v>0.22688939625944049</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1203,13 +1203,13 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>0.67555481129516715</v>
+        <v>0.65576390056044565</v>
       </c>
       <c r="E6">
         <v>0.16544878867935109</v>
       </c>
       <c r="F6">
-        <v>0.20137848676827752</v>
+        <v>0.18158757648083279</v>
       </c>
       <c r="G6">
         <v>4.246322487336681E-2</v>
@@ -1233,7 +1233,7 @@
         <v>2.3043297734159389E-3</v>
       </c>
       <c r="N6">
-        <v>0.22688940007024455</v>
+        <v>0.22688939962296778</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1247,13 +1247,13 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>0.61177267278034497</v>
+        <v>0.60588272705389623</v>
       </c>
       <c r="E7">
         <v>0.16150196149382959</v>
       </c>
       <c r="F7">
-        <v>0.1789987716498937</v>
+        <v>0.17310882605655831</v>
       </c>
       <c r="G7">
         <v>1.285446857063499E-2</v>
@@ -1277,7 +1277,7 @@
         <v>7.0635828026805044E-4</v>
       </c>
       <c r="N7">
-        <v>0.22688940086284659</v>
+        <v>0.22688940072973324</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1291,13 +1291,13 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>0.59327306306753302</v>
+        <v>0.59059134611318487</v>
       </c>
       <c r="E8">
         <v>0.1600401217258294</v>
       </c>
       <c r="F8">
-        <v>0.17248004651096571</v>
+        <v>0.16979832961722441</v>
       </c>
       <c r="G8">
         <v>4.8657565501394832E-3</v>
@@ -1321,7 +1321,7 @@
         <v>2.6033600531852422E-4</v>
       </c>
       <c r="N8">
-        <v>0.22688940109446082</v>
+        <v>0.22688940103385397</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1335,13 +1335,13 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>0.84201361945556263</v>
+        <v>0.78290729817144378</v>
       </c>
       <c r="E9">
         <v>0.1724597851737662</v>
       </c>
       <c r="F9">
-        <v>0.25663076008673746</v>
+        <v>0.19752444013842757</v>
       </c>
       <c r="G9">
         <v>0.12554984313017559</v>
@@ -1365,7 +1365,7 @@
         <v>6.7081842584637607E-3</v>
       </c>
       <c r="N9">
-        <v>0.2268893979326172</v>
+        <v>0.22688939659680835</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1379,13 +1379,13 @@
         <v>20</v>
       </c>
       <c r="D10">
-        <v>0.69963468603116874</v>
+        <v>0.67570011995801516</v>
       </c>
       <c r="E10">
         <v>0.16660936083701461</v>
       </c>
       <c r="F10">
-        <v>0.20722119967257094</v>
+        <v>0.18328663414034052</v>
       </c>
       <c r="G10">
         <v>5.3641455784909607E-2</v>
@@ -1409,7 +1409,7 @@
         <v>2.895531366861593E-3</v>
       </c>
       <c r="N10">
-        <v>0.22688939972714864</v>
+        <v>0.22688939918622547</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1423,13 +1423,13 @@
         <v>21</v>
       </c>
       <c r="D11">
-        <v>0.61326983943335445</v>
+        <v>0.60884375844670302</v>
       </c>
       <c r="E11">
         <v>0.1627298041679664</v>
       </c>
       <c r="F11">
-        <v>0.18025627499179525</v>
+        <v>0.17583019410517342</v>
       </c>
       <c r="G11">
         <v>9.2425664098473061E-3</v>
@@ -1453,7 +1453,7 @@
         <v>5.5341883803508032E-4</v>
       </c>
       <c r="N11">
-        <v>0.2268894008978698</v>
+        <v>0.2268894007978402</v>
       </c>
     </row>
   </sheetData>
@@ -2246,7 +2246,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31E30677-CA83-4A12-8F6E-3C1E599199AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADACB8F-CC89-416F-84FC-414A5512855E}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2259,223 +2259,223 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>83.160296400402231</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>2.2564202334767338</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>0.16682105910435707</v>
       </c>
-      <c r="D2" s="2">
-        <v>22.550325137004286</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.22688939700836835</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.28722738742945769</v>
+      <c r="D2" s="3">
+        <v>28.671696800263796</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.22688939521894802</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.20804991150944696</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>83.410415404273692</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>2.2564202337696266</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>0.16385046828336236</v>
       </c>
-      <c r="D3" s="2">
-        <v>22.94519164078271</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.22688939721581924</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.28084526839092816</v>
+      <c r="D3" s="3">
+        <v>28.98427639282486</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.22688939549954487</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.20490430917779914</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>83.593019857077081</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>2.2564202339690693</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>0.16169295478113721</v>
       </c>
-      <c r="D4" s="2">
-        <v>23.412434322997019</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.22688939741515596</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.2735714350148048</v>
+      <c r="D4" s="3">
+        <v>29.258832120958733</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.22688939580208092</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0.20219679895886142</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>83.839284686069931</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>2.2564202342028365</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>0.15879816340554331</v>
       </c>
-      <c r="D5" s="2">
-        <v>24.11613520712104</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0.22688939769529071</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.26314843079700617</v>
+      <c r="D5" s="3">
+        <v>29.525475055390721</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.22688939625944049</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.19961551831427121</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>85.059064024584131</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>2.2564202358960594</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>0.14470704167423332</v>
       </c>
-      <c r="D6" s="2">
-        <v>29.342840079735101</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.22688940007024455</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.20137848676827752</v>
+      <c r="D6" s="3">
+        <v>31.532448882137786</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0.22688939962296778</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0.18158757648083279</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>85.588391659223575</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>2.2564202365660981</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>0.13871711424406685</v>
       </c>
-      <c r="D7" s="2">
-        <v>31.843273752138927</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.22688940086284659</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.1789987716498937</v>
+      <c r="D7" s="3">
+        <v>32.573804324331988</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.22688940072973324</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0.17310882605655831</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>85.859924725244994</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>2.2564202368574748</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>0.13567307804786299</v>
       </c>
-      <c r="D8" s="2">
-        <v>32.653776953911155</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.22688940109446082</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.17248004651096571</v>
+      <c r="D8" s="3">
+        <v>32.999312042918092</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.22688940103385397</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.16979832961722441</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>83.885665208153142</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>2.2564202343754305</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>0.15825487208025901</v>
       </c>
-      <c r="D9" s="2">
-        <v>24.578078814625311</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.2268893979326172</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.25663076008673746</v>
+      <c r="D9" s="3">
+        <v>29.745070398135482</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.22688939659680835</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.19752444013842757</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>84.688434842286568</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>2.2564202355608156</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>0.14894568979013467</v>
       </c>
-      <c r="D10" s="2">
-        <v>28.753390476707512</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.22688939972714864</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.20722119967257094</v>
+      <c r="D10" s="3">
+        <v>31.331728653143287</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.22688939918622547</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.18328663414034052</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>85.398948865406865</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>2.2564202363792987</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>0.14085233683709486</v>
       </c>
-      <c r="D11" s="2">
-        <v>31.691529937573403</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.2268894008978698</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.18025627499179525</v>
+      <c r="D11" s="3">
+        <v>32.232150743389482</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.2268894007978402</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.17583019410517342</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717BB783-A931-4BFB-AC06-DBEAC39D5932}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D021C9-CED5-4688-93C2-EAC7BBE01862}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D021C9-CED5-4688-93C2-EAC7BBE01862}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C6862C-62D5-4D5B-9542-D2756DF59FC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ammoniaBAU" sheetId="1" r:id="rId1"/>
@@ -156,6 +156,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -201,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -210,6 +211,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1463,10 +1471,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,7 +1506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1532,8 +1540,11 @@
       <c r="K2">
         <v>8.4369931991379321E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N2" s="5"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1567,8 +1578,11 @@
       <c r="K3">
         <v>8.4369936458538186E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N3" s="5"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1602,8 +1616,12 @@
       <c r="K4">
         <v>8.4369940552642131E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="4"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1638,7 +1656,7 @@
         <v>8.4369944081276183E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1673,7 +1691,7 @@
         <v>8.4369972544822147E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1708,7 +1726,7 @@
         <v>8.4369983416892613E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>8.4369986390259444E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1778,7 +1796,7 @@
         <v>8.4369946134882357E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1813,7 +1831,7 @@
         <v>8.4369969227594543E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
